--- a/outputs/CMS_Guia_Operativa_v2.xlsx
+++ b/outputs/CMS_Guia_Operativa_v2.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="Rf7e801571c9a4d4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contenidos" sheetId="2" r:id="R0009065d3ad24927"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectores" sheetId="3" r:id="Raf658e9449a949ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones" sheetId="4" r:id="R8d9105e990ae4d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="5" r:id="Rce78fd2db53e495e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasos" sheetId="6" r:id="Re35ac5d954984832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="7" r:id="Rc770025fcee14378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normas" sheetId="8" r:id="Rfcdf97f6cc2b47f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios" sheetId="9" r:id="R2a41b7a3226041ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria" sheetId="10" r:id="R9a163f10bd4341bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="R21881d74f2f24d4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contenidos" sheetId="2" r:id="R439fcb0a62294f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectores" sheetId="3" r:id="R2f66dd6dc8c540cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones" sheetId="4" r:id="R8fc7c5098b29460b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="5" r:id="R9fe163e952894f63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasos" sheetId="6" r:id="R9c4009c8ef314d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="7" r:id="R104706e1ecef4913"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normas" sheetId="8" r:id="Rccc91794fa8744c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios" sheetId="9" r:id="Recf9a0b087514f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria" sheetId="10" r:id="R9ccba15d76bb4a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanas" sheetId="11" r:id="R6cee23033a8344ca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -50,8 +51,30 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF173F35"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF31594E"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -78,14 +101,87 @@
         <x:fgColor rgb="FFFFF4D6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF006241"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7F3EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF003F2D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF6FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="7">
     <x:border/>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E3DE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7E3DE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E3DE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7E3DE"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE3C7DD"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE3C7DD"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE3C7DD"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE3C7DD"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE3C7DD"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE3C7DD"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE3C7DD"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE3C7DD"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -131,6 +227,43 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -142,7 +275,7 @@
         <x:color rgb="FF006241"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3EA"/>
         </x:patternFill>
       </x:fill>
@@ -153,7 +286,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -842,6 +975,74 @@
         <x:v>Revisar categorías</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>DEPENDENCIAS_CI</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>requirements.txt</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>openpyxl + Pillow + pytest</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>Workflow instala el archivo completo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="23" t="str">
+        <x:v>UNICORN_GRANDE</x:v>
+      </x:c>
+      <x:c r="B13" s="23" t="str">
+        <x:v>1 ruta</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="str">
+        <x:v>Sólo GRANDE</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="str">
+        <x:v>Bloqueado por CMS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="23" t="str">
+        <x:v>CAMPANA_UNICORN</x:v>
+      </x:c>
+      <x:c r="B14" s="23" t="str">
+        <x:v>2026-08-13 a 2026-08-17</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="str">
+        <x:v>Ventana México</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E14" s="23" t="str">
+        <x:v>Configurada en Campanas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="24" t="str">
+        <x:v>TEMPORADA_W33</x:v>
+      </x:c>
+      <x:c r="B15" s="24" t="str">
+        <x:v>8 módulos</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="str">
+        <x:v>8 fichas válidas</x:v>
+      </x:c>
+      <x:c r="D15" s="24" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E15" s="24" t="str">
+        <x:v>Unicorn prioritario; lavanda separada</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
@@ -851,6 +1052,141 @@
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="OK"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="ERROR"/>
   </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="38" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="38" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="26" t="str">
+        <x:v>Campañas · visibilidad temporal</x:v>
+      </x:c>
+      <x:c r="B1" s="26"/>
+      <x:c r="C1" s="26"/>
+      <x:c r="D1" s="26"/>
+      <x:c r="E1" s="26"/>
+      <x:c r="F1" s="26"/>
+      <x:c r="G1" s="26"/>
+      <x:c r="H1" s="26"/>
+      <x:c r="I1" s="26"/>
+      <x:c r="J1" s="26"/>
+      <x:c r="K1" s="26"/>
+      <x:c r="L1" s="26"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="28" t="str">
+        <x:v>La app muestra la campaña sólo dentro de la ventana definida y conserva las recetas fuera de ella.</x:v>
+      </x:c>
+      <x:c r="B2" s="28"/>
+      <x:c r="C2" s="28"/>
+      <x:c r="D2" s="28"/>
+      <x:c r="E2" s="28"/>
+      <x:c r="F2" s="28"/>
+      <x:c r="G2" s="28"/>
+      <x:c r="H2" s="28"/>
+      <x:c r="I2" s="28"/>
+      <x:c r="J2" s="28"/>
+      <x:c r="K2" s="28"/>
+      <x:c r="L2" s="28"/>
+    </x:row>
+    <x:row r="4" ht="26" customHeight="1">
+      <x:c r="A4" s="31" t="str">
+        <x:v>ID_CAMPANA</x:v>
+      </x:c>
+      <x:c r="B4" s="31" t="str">
+        <x:v>TITULO</x:v>
+      </x:c>
+      <x:c r="C4" s="31" t="str">
+        <x:v>SUBTITULO</x:v>
+      </x:c>
+      <x:c r="D4" s="31" t="str">
+        <x:v>FECHA_INICIO</x:v>
+      </x:c>
+      <x:c r="E4" s="31" t="str">
+        <x:v>FECHA_FIN</x:v>
+      </x:c>
+      <x:c r="F4" s="31" t="str">
+        <x:v>ZONA_HORARIA</x:v>
+      </x:c>
+      <x:c r="G4" s="31" t="str">
+        <x:v>ID_PRINCIPAL</x:v>
+      </x:c>
+      <x:c r="H4" s="31" t="str">
+        <x:v>ID_SECUNDARIO</x:v>
+      </x:c>
+      <x:c r="I4" s="31" t="str">
+        <x:v>IMAGEN_CHECKLIST</x:v>
+      </x:c>
+      <x:c r="J4" s="31" t="str">
+        <x:v>IMAGEN_PRACTICAS</x:v>
+      </x:c>
+      <x:c r="K4" s="31" t="str">
+        <x:v>IMAGEN_CONCURSO</x:v>
+      </x:c>
+      <x:c r="L4" s="31" t="str">
+        <x:v>ACTIVO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="48" customHeight="1">
+      <x:c r="A5" s="37" t="str">
+        <x:v>unicorn-agosto</x:v>
+      </x:c>
+      <x:c r="B5" s="38" t="str">
+        <x:v>Semana Unicorn</x:v>
+      </x:c>
+      <x:c r="C5" s="38" t="str">
+        <x:v>Practica Unicorn y Salsa Azul antes del servicio.</x:v>
+      </x:c>
+      <x:c r="D5" s="38" t="str">
+        <x:v>2026-08-13</x:v>
+      </x:c>
+      <x:c r="E5" s="38" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="F5" s="38" t="str">
+        <x:v>America/Mexico_City</x:v>
+      </x:c>
+      <x:c r="G5" s="38" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="H5" s="38" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="I5" s="38" t="str">
+        <x:v>assets/campaigns/unicorn-checklist.webp</x:v>
+      </x:c>
+      <x:c r="J5" s="38" t="str">
+        <x:v>assets/campaigns/unicorn-buenas-practicas.webp</x:v>
+      </x:c>
+      <x:c r="K5" s="38" t="str">
+        <x:v>assets/campaigns/unicorn-concurso.webp</x:v>
+      </x:c>
+      <x:c r="L5" s="39" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -1147,6 +1483,310 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>Temporada · prioridad</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>Salsa Azul Drizzle</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>Prepara el premix azul homogéneo y controla su vida útil de 24 horas.</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>assets/products/temporada/salsa-azul-drizzle.webp</x:v>
+      </x:c>
+      <x:c r="G10" s="22" t="str">
+        <x:v>assets/references/temporada/salsa-azul-drizzle.webp</x:v>
+      </x:c>
+      <x:c r="H10" s="22" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J10" s="22" t="str">
+        <x:v>Ver pestaña Equipo</x:v>
+      </x:c>
+      <x:c r="K10" s="22" t="str">
+        <x:v>Ver pestaña Normas</x:v>
+      </x:c>
+      <x:c r="L10" s="22" t="str">
+        <x:v>size=GRANDE → salsa-azul-drizzle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B11" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="str">
+        <x:v>Temporada · prioridad</x:v>
+      </x:c>
+      <x:c r="D11" s="23" t="str">
+        <x:v>Unicorn Frappuccino</x:v>
+      </x:c>
+      <x:c r="E11" s="23" t="str">
+        <x:v>Práctica guiada del regreso Unicorn. Disponible únicamente en tamaño Grande.</x:v>
+      </x:c>
+      <x:c r="F11" s="23" t="str">
+        <x:v>assets/products/temporada/unicorn-frappuccino.webp</x:v>
+      </x:c>
+      <x:c r="G11" s="23" t="str">
+        <x:v>assets/references/temporada/unicorn-frappuccino.webp</x:v>
+      </x:c>
+      <x:c r="H11" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="I11" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J11" s="23" t="str">
+        <x:v>Ver pestaña Equipo</x:v>
+      </x:c>
+      <x:c r="K11" s="23" t="str">
+        <x:v>Ver pestaña Normas</x:v>
+      </x:c>
+      <x:c r="L11" s="23" t="str">
+        <x:v>size=GRANDE → unicorn-frappuccino</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B12" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="str">
+        <x:v>Lavanda Latte</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="str">
+        <x:v>Espresso, leche y lavanda con acabado aromático.</x:v>
+      </x:c>
+      <x:c r="F12" s="23" t="str">
+        <x:v>assets/products/temporada/lavanda-latte.webp</x:v>
+      </x:c>
+      <x:c r="G12" s="23" t="str">
+        <x:v>assets/references/temporada/lavanda-latte.webp</x:v>
+      </x:c>
+      <x:c r="H12" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="I12" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J12" s="23" t="str">
+        <x:v>Ver pestaña Equipo</x:v>
+      </x:c>
+      <x:c r="K12" s="23" t="str">
+        <x:v>Ver pestaña Normas</x:v>
+      </x:c>
+      <x:c r="L12" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI → lavanda-latte</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B13" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="str">
+        <x:v>Lavanda Latte Helado</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="str">
+        <x:v>Espresso y lavanda sobre leche y hielo.</x:v>
+      </x:c>
+      <x:c r="F13" s="23" t="str">
+        <x:v>assets/products/temporada/lavanda-latte-helado.webp</x:v>
+      </x:c>
+      <x:c r="G13" s="23" t="str">
+        <x:v>assets/references/temporada/lavanda-latte-helado.webp</x:v>
+      </x:c>
+      <x:c r="H13" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="I13" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J13" s="23" t="str">
+        <x:v>Ver pestaña Equipo</x:v>
+      </x:c>
+      <x:c r="K13" s="23" t="str">
+        <x:v>Ver pestaña Normas</x:v>
+      </x:c>
+      <x:c r="L13" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI → lavanda-latte-helado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B14" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="str">
+        <x:v>Lavanda Mocha Blanco Frappuccino</x:v>
+      </x:c>
+      <x:c r="E14" s="23" t="str">
+        <x:v>Frappuccino con mocha blanco, lavanda y base Cream.</x:v>
+      </x:c>
+      <x:c r="F14" s="23" t="str">
+        <x:v>assets/products/temporada/lavanda-mocha-blanco-frappuccino.webp</x:v>
+      </x:c>
+      <x:c r="G14" s="23" t="str">
+        <x:v>assets/references/temporada/lavanda-mocha-blanco-frappuccino.webp</x:v>
+      </x:c>
+      <x:c r="H14" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="I14" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J14" s="23" t="str">
+        <x:v>Ver pestaña Equipo</x:v>
+      </x:c>
+      <x:c r="K14" s="23" t="str">
+        <x:v>Ver pestaña Normas</x:v>
+      </x:c>
+      <x:c r="L14" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI → lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B15" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="D15" s="23" t="str">
+        <x:v>Matcha Lavanda Cold Foam</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="str">
+        <x:v>Matcha helado terminado con cold foam de lavanda.</x:v>
+      </x:c>
+      <x:c r="F15" s="23" t="str">
+        <x:v>assets/products/temporada/matcha-lavanda-cold-foam.webp</x:v>
+      </x:c>
+      <x:c r="G15" s="23" t="str">
+        <x:v>assets/references/temporada/matcha-lavanda-cold-foam.webp</x:v>
+      </x:c>
+      <x:c r="H15" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="I15" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J15" s="23" t="str">
+        <x:v>Ver pestaña Equipo</x:v>
+      </x:c>
+      <x:c r="K15" s="23" t="str">
+        <x:v>Ver pestaña Normas</x:v>
+      </x:c>
+      <x:c r="L15" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI → matcha-lavanda-cold-foam</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B16" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="D16" s="23" t="str">
+        <x:v>Vainilla Lavanda Latte Helado</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="str">
+        <x:v>Espresso, vainilla y lavanda sobre leche y hielo.</x:v>
+      </x:c>
+      <x:c r="F16" s="23" t="str">
+        <x:v>assets/products/temporada/vainilla-lavanda-latte-helado.webp</x:v>
+      </x:c>
+      <x:c r="G16" s="23" t="str">
+        <x:v>assets/references/temporada/vainilla-lavanda-latte-helado.webp</x:v>
+      </x:c>
+      <x:c r="H16" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="I16" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J16" s="23" t="str">
+        <x:v>Ver pestaña Equipo</x:v>
+      </x:c>
+      <x:c r="K16" s="23" t="str">
+        <x:v>Ver pestaña Normas</x:v>
+      </x:c>
+      <x:c r="L16" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI → vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="24" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B17" s="24" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="str">
+        <x:v>Vainilla Lavanda Latte</x:v>
+      </x:c>
+      <x:c r="E17" s="24" t="str">
+        <x:v>Latte caliente con vainilla, lavanda y acabado aromático.</x:v>
+      </x:c>
+      <x:c r="F17" s="24" t="str">
+        <x:v>assets/products/temporada/vainilla-lavanda-latte.webp</x:v>
+      </x:c>
+      <x:c r="G17" s="24" t="str">
+        <x:v>assets/references/temporada/vainilla-lavanda-latte.webp</x:v>
+      </x:c>
+      <x:c r="H17" s="24" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="I17" s="24" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J17" s="24" t="str">
+        <x:v>Ver pestaña Equipo</x:v>
+      </x:c>
+      <x:c r="K17" s="24" t="str">
+        <x:v>Ver pestaña Normas</x:v>
+      </x:c>
+      <x:c r="L17" s="24" t="str">
+        <x:v>ALTO|GRANDE|VENTI → vainilla-lavanda-latte</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
@@ -1294,6 +1934,166 @@
       </x:c>
       <x:c r="F8" s="14" t="n">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>Tamaño</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B10" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C10" s="23" t="str">
+        <x:v>Tamaño</x:v>
+      </x:c>
+      <x:c r="D10" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="F10" s="23" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B11" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="str">
+        <x:v>Tamaño</x:v>
+      </x:c>
+      <x:c r="D11" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="F11" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B12" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="str">
+        <x:v>Tamaño</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="F12" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B13" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="str">
+        <x:v>Tamaño</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="F13" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B14" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="str">
+        <x:v>Tamaño</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="F14" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B15" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="str">
+        <x:v>Tamaño</x:v>
+      </x:c>
+      <x:c r="D15" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="F15" s="23" t="str">
+        <x:v>ALTO|GRANDE|VENTI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="24" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B16" s="24" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="str">
+        <x:v>Tamaño</x:v>
+      </x:c>
+      <x:c r="D16" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="24" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="F16" s="24" t="str">
+        <x:v>ALTO|GRANDE|VENTI</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1582,6 +2382,426 @@
       </x:c>
       <x:c r="G14" s="15" t="str"/>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>Grande</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="22" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="G15" s="22" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B16" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+      <x:c r="D16" s="23" t="str">
+        <x:v>Grande</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="G16" s="23" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B17" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="str">
+        <x:v>ALTO</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="G17" s="23" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B18" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+      <x:c r="D18" s="23" t="str">
+        <x:v>Grande</x:v>
+      </x:c>
+      <x:c r="E18" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F18" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G18" s="23" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B19" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="str">
+        <x:v>VENTI</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="str">
+        <x:v>Venti</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F19" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G19" s="23" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B20" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="str">
+        <x:v>ALTO</x:v>
+      </x:c>
+      <x:c r="D20" s="23" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="G20" s="23" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B21" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="str">
+        <x:v>Grande</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F21" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G21" s="23" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B22" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="str">
+        <x:v>VENTI</x:v>
+      </x:c>
+      <x:c r="D22" s="23" t="str">
+        <x:v>Venti</x:v>
+      </x:c>
+      <x:c r="E22" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F22" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G22" s="23" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B23" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="str">
+        <x:v>ALTO</x:v>
+      </x:c>
+      <x:c r="D23" s="23" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="E23" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="G23" s="23" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B24" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="str">
+        <x:v>Grande</x:v>
+      </x:c>
+      <x:c r="E24" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F24" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G24" s="23" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B25" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="str">
+        <x:v>VENTI</x:v>
+      </x:c>
+      <x:c r="D25" s="23" t="str">
+        <x:v>Venti</x:v>
+      </x:c>
+      <x:c r="E25" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F25" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G25" s="23" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B26" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="str">
+        <x:v>ALTO</x:v>
+      </x:c>
+      <x:c r="D26" s="23" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="E26" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F26" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="G26" s="23" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B27" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="str">
+        <x:v>Grande</x:v>
+      </x:c>
+      <x:c r="E27" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F27" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G27" s="23" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B28" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="str">
+        <x:v>VENTI</x:v>
+      </x:c>
+      <x:c r="D28" s="23" t="str">
+        <x:v>Venti</x:v>
+      </x:c>
+      <x:c r="E28" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F28" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G28" s="23" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B29" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C29" s="23" t="str">
+        <x:v>ALTO</x:v>
+      </x:c>
+      <x:c r="D29" s="23" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="E29" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F29" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="G29" s="23" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B30" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C30" s="23" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+      <x:c r="D30" s="23" t="str">
+        <x:v>Grande</x:v>
+      </x:c>
+      <x:c r="E30" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F30" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G30" s="23" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B31" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C31" s="23" t="str">
+        <x:v>VENTI</x:v>
+      </x:c>
+      <x:c r="D31" s="23" t="str">
+        <x:v>Venti</x:v>
+      </x:c>
+      <x:c r="E31" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F31" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G31" s="23" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B32" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C32" s="23" t="str">
+        <x:v>ALTO</x:v>
+      </x:c>
+      <x:c r="D32" s="23" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="E32" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F32" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="G32" s="23" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B33" s="23" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C33" s="23" t="str">
+        <x:v>GRANDE</x:v>
+      </x:c>
+      <x:c r="D33" s="23" t="str">
+        <x:v>Grande</x:v>
+      </x:c>
+      <x:c r="E33" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F33" s="23" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G33" s="23" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="24" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B34" s="24" t="str">
+        <x:v>size</x:v>
+      </x:c>
+      <x:c r="C34" s="24" t="str">
+        <x:v>VENTI</x:v>
+      </x:c>
+      <x:c r="D34" s="24" t="str">
+        <x:v>Venti</x:v>
+      </x:c>
+      <x:c r="E34" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F34" s="24" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G34" s="24" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -1816,6 +3036,286 @@
         <x:v>croissant</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>size=GRANDE</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="D18" s="22" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B19" s="23" t="str">
+        <x:v>size=GRANDE</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B20" s="23" t="str">
+        <x:v>size=ALTO</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="D20" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B21" s="23" t="str">
+        <x:v>size=GRANDE</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B22" s="23" t="str">
+        <x:v>size=VENTI</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="D22" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B23" s="23" t="str">
+        <x:v>size=ALTO</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="D23" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B24" s="23" t="str">
+        <x:v>size=GRANDE</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B25" s="23" t="str">
+        <x:v>size=VENTI</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="D25" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B26" s="23" t="str">
+        <x:v>size=ALTO</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="D26" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B27" s="23" t="str">
+        <x:v>size=GRANDE</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B28" s="23" t="str">
+        <x:v>size=VENTI</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="D28" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B29" s="23" t="str">
+        <x:v>size=ALTO</x:v>
+      </x:c>
+      <x:c r="C29" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="D29" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B30" s="23" t="str">
+        <x:v>size=GRANDE</x:v>
+      </x:c>
+      <x:c r="C30" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="D30" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B31" s="23" t="str">
+        <x:v>size=VENTI</x:v>
+      </x:c>
+      <x:c r="C31" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="D31" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B32" s="23" t="str">
+        <x:v>size=ALTO</x:v>
+      </x:c>
+      <x:c r="C32" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="D32" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B33" s="23" t="str">
+        <x:v>size=GRANDE</x:v>
+      </x:c>
+      <x:c r="C33" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="D33" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B34" s="23" t="str">
+        <x:v>size=VENTI</x:v>
+      </x:c>
+      <x:c r="C34" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="D34" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B35" s="23" t="str">
+        <x:v>size=ALTO</x:v>
+      </x:c>
+      <x:c r="C35" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="D35" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B36" s="23" t="str">
+        <x:v>size=GRANDE</x:v>
+      </x:c>
+      <x:c r="C36" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="D36" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="24" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B37" s="24" t="str">
+        <x:v>size=VENTI</x:v>
+      </x:c>
+      <x:c r="C37" s="24" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="D37" s="24" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
@@ -3266,6 +4766,1384 @@
       </x:c>
       <x:c r="J49" s="15" t="str"/>
     </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="22" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B50" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C50" s="22" t="str">
+        <x:v>Agrega mocha blanco</x:v>
+      </x:c>
+      <x:c r="D50" s="22" t="str">
+        <x:v>Coloca la salsa de mocha blanco en una jarra vaporizadora.</x:v>
+      </x:c>
+      <x:c r="E50" s="22" t="str">
+        <x:v>sauce</x:v>
+      </x:c>
+      <x:c r="F50" s="22" t="str">
+        <x:v>GRANDE=6 pumps</x:v>
+      </x:c>
+      <x:c r="G50" s="22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H50" s="22" t="str">
+        <x:v>Agrega mocha blanco</x:v>
+      </x:c>
+      <x:c r="I50" s="22" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J50" s="22" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B51" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C51" s="23" t="str">
+        <x:v>Agrega polvo azul</x:v>
+      </x:c>
+      <x:c r="D51" s="23" t="str">
+        <x:v>Añade un sobre completo de polvo azul.</x:v>
+      </x:c>
+      <x:c r="E51" s="23" t="str">
+        <x:v>pour</x:v>
+      </x:c>
+      <x:c r="F51" s="23" t="str">
+        <x:v>GRANDE=1 sobre</x:v>
+      </x:c>
+      <x:c r="G51" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H51" s="23" t="str">
+        <x:v>Agrega polvo azul</x:v>
+      </x:c>
+      <x:c r="I51" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J51" s="23" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B52" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C52" s="23" t="str">
+        <x:v>Integra sin grumos</x:v>
+      </x:c>
+      <x:c r="D52" s="23" t="str">
+        <x:v>Mezcla con la cuchara de Mocha Blanco hasta formar una pasta uniforme.</x:v>
+      </x:c>
+      <x:c r="E52" s="23" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F52" s="23" t="str"/>
+      <x:c r="G52" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H52" s="23" t="str">
+        <x:v>Integra sin grumos</x:v>
+      </x:c>
+      <x:c r="I52" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J52" s="23" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B53" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="23" t="str">
+        <x:v>Agrega mocha blanco</x:v>
+      </x:c>
+      <x:c r="D53" s="23" t="str">
+        <x:v>Añade más salsa de mocha blanco a la misma preparación.</x:v>
+      </x:c>
+      <x:c r="E53" s="23" t="str">
+        <x:v>sauce</x:v>
+      </x:c>
+      <x:c r="F53" s="23" t="str">
+        <x:v>GRANDE=8 pumps</x:v>
+      </x:c>
+      <x:c r="G53" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H53" s="23" t="str">
+        <x:v>Agrega mocha blanco</x:v>
+      </x:c>
+      <x:c r="I53" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J53" s="23" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B54" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C54" s="23" t="str">
+        <x:v>Agrega clásico</x:v>
+      </x:c>
+      <x:c r="D54" s="23" t="str">
+        <x:v>Usa el pump plástico espresso.</x:v>
+      </x:c>
+      <x:c r="E54" s="23" t="str">
+        <x:v>bottle</x:v>
+      </x:c>
+      <x:c r="F54" s="23" t="str">
+        <x:v>GRANDE=6 pumps</x:v>
+      </x:c>
+      <x:c r="G54" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H54" s="23" t="str">
+        <x:v>Agrega clásico</x:v>
+      </x:c>
+      <x:c r="I54" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J54" s="23" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B55" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C55" s="23" t="str">
+        <x:v>Mezcla</x:v>
+      </x:c>
+      <x:c r="D55" s="23" t="str">
+        <x:v>Integra hasta obtener una mezcla homogénea.</x:v>
+      </x:c>
+      <x:c r="E55" s="23" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F55" s="23" t="str"/>
+      <x:c r="G55" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" s="23" t="str">
+        <x:v>Mezcla</x:v>
+      </x:c>
+      <x:c r="I55" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J55" s="23" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B56" s="23" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C56" s="23" t="str">
+        <x:v>Almacena</x:v>
+      </x:c>
+      <x:c r="D56" s="23" t="str">
+        <x:v>Vierte el premix en una mamila plástica, etiqueta y conserva por 24 horas.</x:v>
+      </x:c>
+      <x:c r="E56" s="23" t="str">
+        <x:v>store</x:v>
+      </x:c>
+      <x:c r="F56" s="23" t="str">
+        <x:v>GRANDE=24 horas</x:v>
+      </x:c>
+      <x:c r="G56" s="23" t="n">
+        <x:v>86400</x:v>
+      </x:c>
+      <x:c r="H56" s="23" t="str">
+        <x:v>Conserva</x:v>
+      </x:c>
+      <x:c r="I56" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J56" s="23" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B57" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C57" s="23" t="str">
+        <x:v>Vierte la leche</x:v>
+      </x:c>
+      <x:c r="D57" s="23" t="str">
+        <x:v>Llena hasta la línea inferior del vaso Grande.</x:v>
+      </x:c>
+      <x:c r="E57" s="23" t="str">
+        <x:v>milk</x:v>
+      </x:c>
+      <x:c r="F57" s="23" t="str"/>
+      <x:c r="G57" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H57" s="23" t="str">
+        <x:v>Vierte la leche</x:v>
+      </x:c>
+      <x:c r="I57" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J57" s="23" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B58" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C58" s="23" t="str">
+        <x:v>Pasa a la licuadora</x:v>
+      </x:c>
+      <x:c r="D58" s="23" t="str">
+        <x:v>Vierte el contenido del vaso en el vaso de la licuadora.</x:v>
+      </x:c>
+      <x:c r="E58" s="23" t="str">
+        <x:v>pour</x:v>
+      </x:c>
+      <x:c r="F58" s="23" t="str"/>
+      <x:c r="G58" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58" s="23" t="str">
+        <x:v>Pasa a la licuadora</x:v>
+      </x:c>
+      <x:c r="I58" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J58" s="23" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B59" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C59" s="23" t="str">
+        <x:v>Agrega polvo rosa</x:v>
+      </x:c>
+      <x:c r="D59" s="23" t="str">
+        <x:v>Usa la cuchara de 1 TSP.</x:v>
+      </x:c>
+      <x:c r="E59" s="23" t="str">
+        <x:v>pour</x:v>
+      </x:c>
+      <x:c r="F59" s="23" t="str">
+        <x:v>GRANDE=2 medidas copeteadas</x:v>
+      </x:c>
+      <x:c r="G59" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H59" s="23" t="str">
+        <x:v>Agrega polvo rosa</x:v>
+      </x:c>
+      <x:c r="I59" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J59" s="23" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B60" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="23" t="str">
+        <x:v>Agrega mango</x:v>
+      </x:c>
+      <x:c r="D60" s="23" t="str">
+        <x:v>Usa el pump plástico espresso.</x:v>
+      </x:c>
+      <x:c r="E60" s="23" t="str">
+        <x:v>bottle</x:v>
+      </x:c>
+      <x:c r="F60" s="23" t="str">
+        <x:v>GRANDE=2 pumps</x:v>
+      </x:c>
+      <x:c r="G60" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H60" s="23" t="str">
+        <x:v>Agrega mango</x:v>
+      </x:c>
+      <x:c r="I60" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J60" s="23" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B61" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C61" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="D61" s="23" t="str">
+        <x:v>Usa la medida volumétrica apropiada para Grande.</x:v>
+      </x:c>
+      <x:c r="E61" s="23" t="str">
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="F61" s="23" t="str"/>
+      <x:c r="G61" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="I61" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J61" s="23" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B62" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C62" s="23" t="str">
+        <x:v>Agrega base Cream</x:v>
+      </x:c>
+      <x:c r="D62" s="23" t="str">
+        <x:v>Añade base Cream para Frappuccino.</x:v>
+      </x:c>
+      <x:c r="E62" s="23" t="str">
+        <x:v>bottle</x:v>
+      </x:c>
+      <x:c r="F62" s="23" t="str">
+        <x:v>GRANDE=3 pumps</x:v>
+      </x:c>
+      <x:c r="G62" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62" s="23" t="str">
+        <x:v>Agrega base Cream</x:v>
+      </x:c>
+      <x:c r="I62" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J62" s="23" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B63" s="23" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C63" s="23" t="str">
+        <x:v>Mezcla</x:v>
+      </x:c>
+      <x:c r="D63" s="23" t="str">
+        <x:v>Presiona el botón número 1. No prepares dos bebidas al mismo tiempo.</x:v>
+      </x:c>
+      <x:c r="E63" s="23" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F63" s="23" t="str">
+        <x:v>GRANDE=Botón 1</x:v>
+      </x:c>
+      <x:c r="G63" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H63" s="23" t="str">
+        <x:v>Mezcla</x:v>
+      </x:c>
+      <x:c r="I63" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J63" s="23" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B64" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C64" s="23" t="str">
+        <x:v>Forma la espiral azul</x:v>
+      </x:c>
+      <x:c r="D64" s="23" t="str">
+        <x:v>Agrega una espiral de Salsa Azul Drizzle alrededor de la línea superior del vaso.</x:v>
+      </x:c>
+      <x:c r="E64" s="23" t="str">
+        <x:v>sauce</x:v>
+      </x:c>
+      <x:c r="F64" s="23" t="str">
+        <x:v>GRANDE=1 espiral</x:v>
+      </x:c>
+      <x:c r="G64" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H64" s="23" t="str">
+        <x:v>Forma la espiral azul</x:v>
+      </x:c>
+      <x:c r="I64" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J64" s="23" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B65" s="23" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C65" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="D65" s="23" t="str">
+        <x:v>Vierte a 1 cm del borde, agrega 2½ vueltas de crema batida, espolvorea azul y rosa 3 veces cada uno, coloca tapa domo y popote.</x:v>
+      </x:c>
+      <x:c r="E65" s="23" t="str">
+        <x:v>serve</x:v>
+      </x:c>
+      <x:c r="F65" s="23" t="str">
+        <x:v>GRANDE=2½ vueltas + 3/3</x:v>
+      </x:c>
+      <x:c r="G65" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="I65" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J65" s="23" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B66" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C66" s="23" t="str">
+        <x:v>Vaporiza la leche</x:v>
+      </x:c>
+      <x:c r="D66" s="23" t="str">
+        <x:v>Vaporiza la leche a la temperatura correspondiente.</x:v>
+      </x:c>
+      <x:c r="E66" s="23" t="str">
+        <x:v>heat</x:v>
+      </x:c>
+      <x:c r="F66" s="23" t="str"/>
+      <x:c r="G66" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H66" s="23" t="str">
+        <x:v>Vaporiza la leche</x:v>
+      </x:c>
+      <x:c r="I66" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J66" s="23" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B67" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C67" s="23" t="str">
+        <x:v>Agrega espresso</x:v>
+      </x:c>
+      <x:c r="D67" s="23" t="str">
+        <x:v>Sirve los shots en el vaso.</x:v>
+      </x:c>
+      <x:c r="E67" s="23" t="str">
+        <x:v>coffee</x:v>
+      </x:c>
+      <x:c r="F67" s="23" t="str">
+        <x:v>ALTO=1 shot|GRANDE=2 shots|VENTI=2 shots</x:v>
+      </x:c>
+      <x:c r="G67" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H67" s="23" t="str">
+        <x:v>Agrega espresso</x:v>
+      </x:c>
+      <x:c r="I67" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J67" s="23" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B68" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C68" s="23" t="str">
+        <x:v>Agrega lavanda</x:v>
+      </x:c>
+      <x:c r="D68" s="23" t="str">
+        <x:v>Incorpora el polvo de lavanda y mezcla.</x:v>
+      </x:c>
+      <x:c r="E68" s="23" t="str">
+        <x:v>pour</x:v>
+      </x:c>
+      <x:c r="F68" s="23" t="str">
+        <x:v>ALTO=3 medidas|GRANDE=4 medidas|VENTI=5 medidas</x:v>
+      </x:c>
+      <x:c r="G68" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H68" s="23" t="str">
+        <x:v>Agrega lavanda</x:v>
+      </x:c>
+      <x:c r="I68" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J68" s="23" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B69" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C69" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="D69" s="23" t="str">
+        <x:v>Vierte leche a 6 mm del borde y espolvorea lavanda cuatro veces.</x:v>
+      </x:c>
+      <x:c r="E69" s="23" t="str">
+        <x:v>serve</x:v>
+      </x:c>
+      <x:c r="F69" s="23" t="str">
+        <x:v>TODOS=4 veces</x:v>
+      </x:c>
+      <x:c r="G69" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H69" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="I69" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J69" s="23" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B70" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C70" s="23" t="str">
+        <x:v>Agrega espresso</x:v>
+      </x:c>
+      <x:c r="D70" s="23" t="str">
+        <x:v>Sirve los shots en el vaso.</x:v>
+      </x:c>
+      <x:c r="E70" s="23" t="str">
+        <x:v>coffee</x:v>
+      </x:c>
+      <x:c r="F70" s="23" t="str">
+        <x:v>ALTO=1 shot|GRANDE=2 shots|VENTI=2 shots</x:v>
+      </x:c>
+      <x:c r="G70" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H70" s="23" t="str">
+        <x:v>Agrega espresso</x:v>
+      </x:c>
+      <x:c r="I70" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J70" s="23" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B71" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C71" s="23" t="str">
+        <x:v>Agrega lavanda</x:v>
+      </x:c>
+      <x:c r="D71" s="23" t="str">
+        <x:v>Mezcla espresso, polvo de lavanda y leche hasta la línea superior.</x:v>
+      </x:c>
+      <x:c r="E71" s="23" t="str">
+        <x:v>pour</x:v>
+      </x:c>
+      <x:c r="F71" s="23" t="str">
+        <x:v>ALTO=3 medidas|GRANDE=4 medidas|VENTI=5 medidas</x:v>
+      </x:c>
+      <x:c r="G71" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H71" s="23" t="str">
+        <x:v>Agrega lavanda</x:v>
+      </x:c>
+      <x:c r="I71" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J71" s="23" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B72" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C72" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="D72" s="23" t="str">
+        <x:v>Llena con hielo hasta 6 mm debajo del borde.</x:v>
+      </x:c>
+      <x:c r="E72" s="23" t="str">
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="F72" s="23" t="str"/>
+      <x:c r="G72" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H72" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="I72" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J72" s="23" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B73" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C73" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="D73" s="23" t="str">
+        <x:v>Espolvorea lavanda cuatro veces y coloca tapa Nitro.</x:v>
+      </x:c>
+      <x:c r="E73" s="23" t="str">
+        <x:v>serve</x:v>
+      </x:c>
+      <x:c r="F73" s="23" t="str">
+        <x:v>TODOS=4 veces</x:v>
+      </x:c>
+      <x:c r="G73" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H73" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="I73" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J73" s="23" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B74" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C74" s="23" t="str">
+        <x:v>Vierte la leche</x:v>
+      </x:c>
+      <x:c r="D74" s="23" t="str">
+        <x:v>Llena hasta la línea inferior y pasa a la licuadora.</x:v>
+      </x:c>
+      <x:c r="E74" s="23" t="str">
+        <x:v>milk</x:v>
+      </x:c>
+      <x:c r="F74" s="23" t="str"/>
+      <x:c r="G74" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H74" s="23" t="str">
+        <x:v>Vierte la leche</x:v>
+      </x:c>
+      <x:c r="I74" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J74" s="23" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B75" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C75" s="23" t="str">
+        <x:v>Agrega mocha blanco</x:v>
+      </x:c>
+      <x:c r="D75" s="23" t="str">
+        <x:v>Usa pump metal o la equivalencia CBS.</x:v>
+      </x:c>
+      <x:c r="E75" s="23" t="str">
+        <x:v>sauce</x:v>
+      </x:c>
+      <x:c r="F75" s="23" t="str">
+        <x:v>ALTO=1 metal / 2 CBS|GRANDE=2 metal / 3 CBS|VENTI=2 metal / 4 CBS</x:v>
+      </x:c>
+      <x:c r="G75" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H75" s="23" t="str">
+        <x:v>Agrega mocha blanco</x:v>
+      </x:c>
+      <x:c r="I75" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J75" s="23" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B76" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C76" s="23" t="str">
+        <x:v>Agrega lavanda</x:v>
+      </x:c>
+      <x:c r="D76" s="23" t="str">
+        <x:v>Añade polvo de lavanda.</x:v>
+      </x:c>
+      <x:c r="E76" s="23" t="str">
+        <x:v>pour</x:v>
+      </x:c>
+      <x:c r="F76" s="23" t="str">
+        <x:v>ALTO=2 medidas|GRANDE=3 medidas|VENTI=4 medidas</x:v>
+      </x:c>
+      <x:c r="G76" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H76" s="23" t="str">
+        <x:v>Agrega lavanda</x:v>
+      </x:c>
+      <x:c r="I76" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J76" s="23" t="str"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B77" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C77" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="D77" s="23" t="str">
+        <x:v>Usa la medida volumétrica apropiada.</x:v>
+      </x:c>
+      <x:c r="E77" s="23" t="str">
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="F77" s="23" t="str"/>
+      <x:c r="G77" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H77" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="I77" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J77" s="23" t="str"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B78" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C78" s="23" t="str">
+        <x:v>Agrega base Cream</x:v>
+      </x:c>
+      <x:c r="D78" s="23" t="str">
+        <x:v>Añade base Cream para Frappuccino.</x:v>
+      </x:c>
+      <x:c r="E78" s="23" t="str">
+        <x:v>bottle</x:v>
+      </x:c>
+      <x:c r="F78" s="23" t="str">
+        <x:v>ALTO=2 pumps|GRANDE=3 pumps|VENTI=4 pumps</x:v>
+      </x:c>
+      <x:c r="G78" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H78" s="23" t="str">
+        <x:v>Agrega base Cream</x:v>
+      </x:c>
+      <x:c r="I78" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J78" s="23" t="str"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B79" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C79" s="23" t="str">
+        <x:v>Mezcla</x:v>
+      </x:c>
+      <x:c r="D79" s="23" t="str">
+        <x:v>Presiona el botón número 1.</x:v>
+      </x:c>
+      <x:c r="E79" s="23" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F79" s="23" t="str">
+        <x:v>TODOS=Botón 1</x:v>
+      </x:c>
+      <x:c r="G79" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H79" s="23" t="str">
+        <x:v>Mezcla</x:v>
+      </x:c>
+      <x:c r="I79" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J79" s="23" t="str"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B80" s="23" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C80" s="23" t="str">
+        <x:v>Vierte</x:v>
+      </x:c>
+      <x:c r="D80" s="23" t="str">
+        <x:v>Sirve hasta 1 cm debajo del borde.</x:v>
+      </x:c>
+      <x:c r="E80" s="23" t="str">
+        <x:v>pour</x:v>
+      </x:c>
+      <x:c r="F80" s="23" t="str"/>
+      <x:c r="G80" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H80" s="23" t="str">
+        <x:v>Vierte</x:v>
+      </x:c>
+      <x:c r="I80" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J80" s="23" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B81" s="23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C81" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="D81" s="23" t="str">
+        <x:v>Cubre con crema batida, espolvorea lavanda cuatro veces y coloca tapa domo.</x:v>
+      </x:c>
+      <x:c r="E81" s="23" t="str">
+        <x:v>serve</x:v>
+      </x:c>
+      <x:c r="F81" s="23" t="str">
+        <x:v>TODOS=4 veces</x:v>
+      </x:c>
+      <x:c r="G81" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H81" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="I81" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J81" s="23" t="str"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B82" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C82" s="23" t="str">
+        <x:v>Prepara el cold foam</x:v>
+      </x:c>
+      <x:c r="D82" s="23" t="str">
+        <x:v>Mezcla 100 ml de crema dulce de vainilla con lavanda y presiona botón 3.</x:v>
+      </x:c>
+      <x:c r="E82" s="23" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F82" s="23" t="str">
+        <x:v>TODOS=100 ml + 2 cucharadas; botón 3</x:v>
+      </x:c>
+      <x:c r="G82" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82" s="23" t="str">
+        <x:v>Prepara el cold foam</x:v>
+      </x:c>
+      <x:c r="I82" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J82" s="23" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B83" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C83" s="23" t="str">
+        <x:v>Prepara la base</x:v>
+      </x:c>
+      <x:c r="D83" s="23" t="str">
+        <x:v>Agrega agua a la línea alta de la coctelera, jarabe clásico y matcha.</x:v>
+      </x:c>
+      <x:c r="E83" s="23" t="str">
+        <x:v>water</x:v>
+      </x:c>
+      <x:c r="F83" s="23" t="str">
+        <x:v>ALTO=3 clásico + 2 matcha|GRANDE=4 clásico + 3 matcha|VENTI=5 clásico + 4 matcha</x:v>
+      </x:c>
+      <x:c r="G83" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="23" t="str">
+        <x:v>Prepara la base</x:v>
+      </x:c>
+      <x:c r="I83" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J83" s="23" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B84" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C84" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="D84" s="23" t="str">
+        <x:v>Usa la medida volumétrica apropiada.</x:v>
+      </x:c>
+      <x:c r="E84" s="23" t="str">
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="F84" s="23" t="str"/>
+      <x:c r="G84" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="I84" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J84" s="23" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B85" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C85" s="23" t="str">
+        <x:v>Agita y sirve</x:v>
+      </x:c>
+      <x:c r="D85" s="23" t="str">
+        <x:v>Agita diez veces y vierte en el vaso.</x:v>
+      </x:c>
+      <x:c r="E85" s="23" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F85" s="23" t="str">
+        <x:v>TODOS=10 veces</x:v>
+      </x:c>
+      <x:c r="G85" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H85" s="23" t="str">
+        <x:v>Agita y sirve</x:v>
+      </x:c>
+      <x:c r="I85" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J85" s="23" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B86" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C86" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="D86" s="23" t="str">
+        <x:v>Agrega leche a 2 cm del borde y cold foam hasta 6 mm debajo del borde.</x:v>
+      </x:c>
+      <x:c r="E86" s="23" t="str">
+        <x:v>serve</x:v>
+      </x:c>
+      <x:c r="F86" s="23" t="str"/>
+      <x:c r="G86" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H86" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="I86" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J86" s="23" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B87" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C87" s="23" t="str">
+        <x:v>Agrega espresso</x:v>
+      </x:c>
+      <x:c r="D87" s="23" t="str">
+        <x:v>Sirve los shots en el vaso.</x:v>
+      </x:c>
+      <x:c r="E87" s="23" t="str">
+        <x:v>coffee</x:v>
+      </x:c>
+      <x:c r="F87" s="23" t="str">
+        <x:v>ALTO=1 shot|GRANDE=2 shots|VENTI=2 shots</x:v>
+      </x:c>
+      <x:c r="G87" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H87" s="23" t="str">
+        <x:v>Agrega espresso</x:v>
+      </x:c>
+      <x:c r="I87" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J87" s="23" t="str"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B88" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C88" s="23" t="str">
+        <x:v>Agrega sabores</x:v>
+      </x:c>
+      <x:c r="D88" s="23" t="str">
+        <x:v>Añade vainilla y polvo de lavanda.</x:v>
+      </x:c>
+      <x:c r="E88" s="23" t="str">
+        <x:v>bottle</x:v>
+      </x:c>
+      <x:c r="F88" s="23" t="str">
+        <x:v>ALTO=3 vainilla + 2 lavanda|GRANDE=4 vainilla + 3 lavanda|VENTI=5 vainilla + 4 lavanda</x:v>
+      </x:c>
+      <x:c r="G88" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88" s="23" t="str">
+        <x:v>Agrega sabores</x:v>
+      </x:c>
+      <x:c r="I88" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J88" s="23" t="str"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B89" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C89" s="23" t="str">
+        <x:v>Agrega leche</x:v>
+      </x:c>
+      <x:c r="D89" s="23" t="str">
+        <x:v>Vierte leche fría hasta la línea superior.</x:v>
+      </x:c>
+      <x:c r="E89" s="23" t="str">
+        <x:v>milk</x:v>
+      </x:c>
+      <x:c r="F89" s="23" t="str"/>
+      <x:c r="G89" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H89" s="23" t="str">
+        <x:v>Agrega leche</x:v>
+      </x:c>
+      <x:c r="I89" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J89" s="23" t="str"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B90" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C90" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="D90" s="23" t="str">
+        <x:v>Llena con hielo hasta 6 mm debajo del borde.</x:v>
+      </x:c>
+      <x:c r="E90" s="23" t="str">
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="F90" s="23" t="str"/>
+      <x:c r="G90" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H90" s="23" t="str">
+        <x:v>Agrega hielo</x:v>
+      </x:c>
+      <x:c r="I90" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J90" s="23" t="str"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B91" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C91" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="D91" s="23" t="str">
+        <x:v>Espolvorea lavanda cuatro veces y coloca tapa Nitro.</x:v>
+      </x:c>
+      <x:c r="E91" s="23" t="str">
+        <x:v>serve</x:v>
+      </x:c>
+      <x:c r="F91" s="23" t="str">
+        <x:v>TODOS=4 veces</x:v>
+      </x:c>
+      <x:c r="G91" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H91" s="23" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="I91" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J91" s="23" t="str"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B92" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C92" s="23" t="str">
+        <x:v>Vaporiza la leche</x:v>
+      </x:c>
+      <x:c r="D92" s="23" t="str">
+        <x:v>Vaporiza la leche a la temperatura correspondiente.</x:v>
+      </x:c>
+      <x:c r="E92" s="23" t="str">
+        <x:v>heat</x:v>
+      </x:c>
+      <x:c r="F92" s="23" t="str"/>
+      <x:c r="G92" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H92" s="23" t="str">
+        <x:v>Vaporiza la leche</x:v>
+      </x:c>
+      <x:c r="I92" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J92" s="23" t="str"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B93" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C93" s="23" t="str">
+        <x:v>Agrega espresso</x:v>
+      </x:c>
+      <x:c r="D93" s="23" t="str">
+        <x:v>Sirve los shots en el vaso.</x:v>
+      </x:c>
+      <x:c r="E93" s="23" t="str">
+        <x:v>coffee</x:v>
+      </x:c>
+      <x:c r="F93" s="23" t="str">
+        <x:v>ALTO=1 shot|GRANDE=2 shots|VENTI=2 shots</x:v>
+      </x:c>
+      <x:c r="G93" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H93" s="23" t="str">
+        <x:v>Agrega espresso</x:v>
+      </x:c>
+      <x:c r="I93" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J93" s="23" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B94" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C94" s="23" t="str">
+        <x:v>Agrega sabores</x:v>
+      </x:c>
+      <x:c r="D94" s="23" t="str">
+        <x:v>Añade vainilla y polvo de lavanda.</x:v>
+      </x:c>
+      <x:c r="E94" s="23" t="str">
+        <x:v>bottle</x:v>
+      </x:c>
+      <x:c r="F94" s="23" t="str">
+        <x:v>ALTO=3 vainilla + 2 lavanda|GRANDE=4 vainilla + 3 lavanda|VENTI=5 vainilla + 4 lavanda</x:v>
+      </x:c>
+      <x:c r="G94" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H94" s="23" t="str">
+        <x:v>Agrega sabores</x:v>
+      </x:c>
+      <x:c r="I94" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J94" s="23" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B95" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C95" s="23" t="str">
+        <x:v>Mezcla</x:v>
+      </x:c>
+      <x:c r="D95" s="23" t="str">
+        <x:v>Integra espresso, vainilla y lavanda.</x:v>
+      </x:c>
+      <x:c r="E95" s="23" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F95" s="23" t="str"/>
+      <x:c r="G95" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H95" s="23" t="str">
+        <x:v>Mezcla</x:v>
+      </x:c>
+      <x:c r="I95" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J95" s="23" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="24" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B96" s="24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C96" s="24" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="D96" s="24" t="str">
+        <x:v>Vierte leche a 6 mm del borde y espolvorea lavanda cuatro veces.</x:v>
+      </x:c>
+      <x:c r="E96" s="24" t="str">
+        <x:v>serve</x:v>
+      </x:c>
+      <x:c r="F96" s="24" t="str">
+        <x:v>TODOS=4 veces</x:v>
+      </x:c>
+      <x:c r="G96" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H96" s="24" t="str">
+        <x:v>Termina</x:v>
+      </x:c>
+      <x:c r="I96" s="24" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="J96" s="24" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
@@ -3573,6 +6451,370 @@
         <x:v>SI</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="22" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B23" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="str">
+        <x:v>Jarra vaporizadora</x:v>
+      </x:c>
+      <x:c r="D23" s="22" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B24" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="str">
+        <x:v>Dosificador metal para Mocha Blanco</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B25" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="str">
+        <x:v>Cuchara para Mocha Blanco</x:v>
+      </x:c>
+      <x:c r="D25" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B26" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="str">
+        <x:v>Mamila plástica</x:v>
+      </x:c>
+      <x:c r="D26" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B27" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="str">
+        <x:v>Vaso Grande</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B28" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="str">
+        <x:v>Vaso de licuadora</x:v>
+      </x:c>
+      <x:c r="D28" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B29" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C29" s="23" t="str">
+        <x:v>Cuchara de 1 TSP</x:v>
+      </x:c>
+      <x:c r="D29" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B30" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="23" t="str">
+        <x:v>Mamila con Salsa Azul Drizzle</x:v>
+      </x:c>
+      <x:c r="D30" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B31" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C31" s="23" t="str">
+        <x:v>Vaso caliente</x:v>
+      </x:c>
+      <x:c r="D31" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B32" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C32" s="23" t="str">
+        <x:v>Jarra para leche</x:v>
+      </x:c>
+      <x:c r="D32" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B33" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C33" s="23" t="str">
+        <x:v>Espolvoreador de lavanda</x:v>
+      </x:c>
+      <x:c r="D33" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B34" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" s="23" t="str">
+        <x:v>Vaso frío</x:v>
+      </x:c>
+      <x:c r="D34" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B35" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C35" s="23" t="str">
+        <x:v>Tapa Nitro</x:v>
+      </x:c>
+      <x:c r="D35" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B36" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C36" s="23" t="str">
+        <x:v>Espolvoreador de lavanda</x:v>
+      </x:c>
+      <x:c r="D36" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B37" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C37" s="23" t="str">
+        <x:v>Vaso frío</x:v>
+      </x:c>
+      <x:c r="D37" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B38" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C38" s="23" t="str">
+        <x:v>Licuadora</x:v>
+      </x:c>
+      <x:c r="D38" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B39" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C39" s="23" t="str">
+        <x:v>Tapa domo</x:v>
+      </x:c>
+      <x:c r="D39" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B40" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C40" s="23" t="str">
+        <x:v>Coctelera</x:v>
+      </x:c>
+      <x:c r="D40" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B41" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C41" s="23" t="str">
+        <x:v>Licuadora para cold foam</x:v>
+      </x:c>
+      <x:c r="D41" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B42" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C42" s="23" t="str">
+        <x:v>Vaso frío</x:v>
+      </x:c>
+      <x:c r="D42" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B43" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C43" s="23" t="str">
+        <x:v>Vaso frío</x:v>
+      </x:c>
+      <x:c r="D43" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B44" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C44" s="23" t="str">
+        <x:v>Tapa Nitro</x:v>
+      </x:c>
+      <x:c r="D44" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B45" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C45" s="23" t="str">
+        <x:v>Espolvoreador de lavanda</x:v>
+      </x:c>
+      <x:c r="D45" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B46" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C46" s="23" t="str">
+        <x:v>Vaso caliente</x:v>
+      </x:c>
+      <x:c r="D46" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B47" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C47" s="23" t="str">
+        <x:v>Jarra para leche</x:v>
+      </x:c>
+      <x:c r="D47" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="24" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B48" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C48" s="24" t="str">
+        <x:v>Espolvoreador de lavanda</x:v>
+      </x:c>
+      <x:c r="D48" s="24" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
@@ -3709,6 +6951,342 @@
         <x:v>Mantén el producto congelado a -18 °C hasta su preparación.</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>Usar únicamente en tamaño Grande.</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B12" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="str">
+        <x:v>Vida útil: 24 horas.</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="23" t="str">
+        <x:v>salsa-azul-drizzle</x:v>
+      </x:c>
+      <x:c r="B13" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="str">
+        <x:v>La mezcla debe quedar homogénea y sin grumos.</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B14" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="str">
+        <x:v>Disponible del 15 al 17 de agosto y sólo en tamaño Grande.</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B15" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="str">
+        <x:v>No preparar dos bebidas al mismo tiempo en la licuadora.</x:v>
+      </x:c>
+      <x:c r="D15" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="23" t="str">
+        <x:v>unicorn-frappuccino</x:v>
+      </x:c>
+      <x:c r="B16" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="str">
+        <x:v>Verificar Salsa Azul Drizzle vigente antes de iniciar.</x:v>
+      </x:c>
+      <x:c r="D16" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B17" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="str">
+        <x:v>Confirmar el tamaño antes de iniciar.</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B18" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="str">
+        <x:v>Seguir la secuencia sin omitir pasos.</x:v>
+      </x:c>
+      <x:c r="D18" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="23" t="str">
+        <x:v>lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B19" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="str">
+        <x:v>Usar la ficha original como referencia visual.</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B20" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="str">
+        <x:v>Confirmar el tamaño antes de iniciar.</x:v>
+      </x:c>
+      <x:c r="D20" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B21" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="str">
+        <x:v>Seguir la secuencia sin omitir pasos.</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="23" t="str">
+        <x:v>lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B22" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="str">
+        <x:v>Usar la ficha original como referencia visual.</x:v>
+      </x:c>
+      <x:c r="D22" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B23" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="str">
+        <x:v>Confirmar el tamaño antes de iniciar.</x:v>
+      </x:c>
+      <x:c r="D23" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B24" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="str">
+        <x:v>Seguir la secuencia sin omitir pasos.</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="23" t="str">
+        <x:v>lavanda-mocha-blanco-frappuccino</x:v>
+      </x:c>
+      <x:c r="B25" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="str">
+        <x:v>Usar la ficha original como referencia visual.</x:v>
+      </x:c>
+      <x:c r="D25" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B26" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="str">
+        <x:v>Confirmar el tamaño antes de iniciar.</x:v>
+      </x:c>
+      <x:c r="D26" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B27" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="str">
+        <x:v>Seguir la secuencia sin omitir pasos.</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="23" t="str">
+        <x:v>matcha-lavanda-cold-foam</x:v>
+      </x:c>
+      <x:c r="B28" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="str">
+        <x:v>Usar la ficha original como referencia visual.</x:v>
+      </x:c>
+      <x:c r="D28" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B29" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C29" s="23" t="str">
+        <x:v>Confirmar el tamaño antes de iniciar.</x:v>
+      </x:c>
+      <x:c r="D29" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B30" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C30" s="23" t="str">
+        <x:v>Seguir la secuencia sin omitir pasos.</x:v>
+      </x:c>
+      <x:c r="D30" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="23" t="str">
+        <x:v>vainilla-lavanda-latte-helado</x:v>
+      </x:c>
+      <x:c r="B31" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C31" s="23" t="str">
+        <x:v>Usar la ficha original como referencia visual.</x:v>
+      </x:c>
+      <x:c r="D31" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B32" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C32" s="23" t="str">
+        <x:v>Confirmar el tamaño antes de iniciar.</x:v>
+      </x:c>
+      <x:c r="D32" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="23" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B33" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C33" s="23" t="str">
+        <x:v>Seguir la secuencia sin omitir pasos.</x:v>
+      </x:c>
+      <x:c r="D33" s="23" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="24" t="str">
+        <x:v>vainilla-lavanda-latte</x:v>
+      </x:c>
+      <x:c r="B34" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C34" s="24" t="str">
+        <x:v>Usar la ficha original como referencia visual.</x:v>
+      </x:c>
+      <x:c r="D34" s="24" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
@@ -5927,6 +9505,214 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="22" t="str">
+        <x:v>temporada-practica-01</x:v>
+      </x:c>
+      <x:c r="B87" s="22" t="str">
+        <x:v>Salsa Azul Drizzle</x:v>
+      </x:c>
+      <x:c r="C87" s="22" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="D87" s="22" t="str">
+        <x:v>Temporada · prioridad</x:v>
+      </x:c>
+      <x:c r="E87" s="22" t="str">
+        <x:v>assets/products/temporada/salsa-azul-drizzle.webp</x:v>
+      </x:c>
+      <x:c r="F87" s="22" t="str">
+        <x:v>assets/references/temporada/salsa-azul-drizzle.webp</x:v>
+      </x:c>
+      <x:c r="G87" s="22" t="str">
+        <x:v>Bebidas Temporada · W33</x:v>
+      </x:c>
+      <x:c r="H87" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="23" t="str">
+        <x:v>temporada-practica-02</x:v>
+      </x:c>
+      <x:c r="B88" s="23" t="str">
+        <x:v>Unicorn Frappuccino</x:v>
+      </x:c>
+      <x:c r="C88" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="D88" s="23" t="str">
+        <x:v>Temporada · prioridad</x:v>
+      </x:c>
+      <x:c r="E88" s="23" t="str">
+        <x:v>assets/products/temporada/unicorn-frappuccino.webp</x:v>
+      </x:c>
+      <x:c r="F88" s="23" t="str">
+        <x:v>assets/references/temporada/unicorn-frappuccino.webp</x:v>
+      </x:c>
+      <x:c r="G88" s="23" t="str">
+        <x:v>Bebidas Temporada · W33</x:v>
+      </x:c>
+      <x:c r="H88" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="23" t="str">
+        <x:v>temporada-practica-03</x:v>
+      </x:c>
+      <x:c r="B89" s="23" t="str">
+        <x:v>Lavanda Latte</x:v>
+      </x:c>
+      <x:c r="C89" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="D89" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="E89" s="23" t="str">
+        <x:v>assets/products/temporada/lavanda-latte.webp</x:v>
+      </x:c>
+      <x:c r="F89" s="23" t="str">
+        <x:v>assets/references/temporada/lavanda-latte.webp</x:v>
+      </x:c>
+      <x:c r="G89" s="23" t="str">
+        <x:v>Bebidas Temporada · W33</x:v>
+      </x:c>
+      <x:c r="H89" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="23" t="str">
+        <x:v>temporada-practica-04</x:v>
+      </x:c>
+      <x:c r="B90" s="23" t="str">
+        <x:v>Lavanda Latte Helado</x:v>
+      </x:c>
+      <x:c r="C90" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="D90" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="E90" s="23" t="str">
+        <x:v>assets/products/temporada/lavanda-latte-helado.webp</x:v>
+      </x:c>
+      <x:c r="F90" s="23" t="str">
+        <x:v>assets/references/temporada/lavanda-latte-helado.webp</x:v>
+      </x:c>
+      <x:c r="G90" s="23" t="str">
+        <x:v>Bebidas Temporada · W33</x:v>
+      </x:c>
+      <x:c r="H90" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="23" t="str">
+        <x:v>temporada-practica-05</x:v>
+      </x:c>
+      <x:c r="B91" s="23" t="str">
+        <x:v>Lavanda Mocha Blanco Frappuccino</x:v>
+      </x:c>
+      <x:c r="C91" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="D91" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="E91" s="23" t="str">
+        <x:v>assets/products/temporada/lavanda-mocha-blanco-frappuccino.webp</x:v>
+      </x:c>
+      <x:c r="F91" s="23" t="str">
+        <x:v>assets/references/temporada/lavanda-mocha-blanco-frappuccino.webp</x:v>
+      </x:c>
+      <x:c r="G91" s="23" t="str">
+        <x:v>Bebidas Temporada · W33</x:v>
+      </x:c>
+      <x:c r="H91" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="23" t="str">
+        <x:v>temporada-practica-06</x:v>
+      </x:c>
+      <x:c r="B92" s="23" t="str">
+        <x:v>Matcha Lavanda Cold Foam</x:v>
+      </x:c>
+      <x:c r="C92" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="D92" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="E92" s="23" t="str">
+        <x:v>assets/products/temporada/matcha-lavanda-cold-foam.webp</x:v>
+      </x:c>
+      <x:c r="F92" s="23" t="str">
+        <x:v>assets/references/temporada/matcha-lavanda-cold-foam.webp</x:v>
+      </x:c>
+      <x:c r="G92" s="23" t="str">
+        <x:v>Bebidas Temporada · W33</x:v>
+      </x:c>
+      <x:c r="H92" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="23" t="str">
+        <x:v>temporada-practica-07</x:v>
+      </x:c>
+      <x:c r="B93" s="23" t="str">
+        <x:v>Vainilla Lavanda Latte Helado</x:v>
+      </x:c>
+      <x:c r="C93" s="23" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="D93" s="23" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="E93" s="23" t="str">
+        <x:v>assets/products/temporada/vainilla-lavanda-latte-helado.webp</x:v>
+      </x:c>
+      <x:c r="F93" s="23" t="str">
+        <x:v>assets/references/temporada/vainilla-lavanda-latte-helado.webp</x:v>
+      </x:c>
+      <x:c r="G93" s="23" t="str">
+        <x:v>Bebidas Temporada · W33</x:v>
+      </x:c>
+      <x:c r="H93" s="23" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="24" t="str">
+        <x:v>temporada-practica-08</x:v>
+      </x:c>
+      <x:c r="B94" s="24" t="str">
+        <x:v>Vainilla Lavanda Latte</x:v>
+      </x:c>
+      <x:c r="C94" s="24" t="str">
+        <x:v>Bebidas</x:v>
+      </x:c>
+      <x:c r="D94" s="24" t="str">
+        <x:v>Temporada · lavanda</x:v>
+      </x:c>
+      <x:c r="E94" s="24" t="str">
+        <x:v>assets/products/temporada/vainilla-lavanda-latte.webp</x:v>
+      </x:c>
+      <x:c r="F94" s="24" t="str">
+        <x:v>assets/references/temporada/vainilla-lavanda-latte.webp</x:v>
+      </x:c>
+      <x:c r="G94" s="24" t="str">
+        <x:v>Bebidas Temporada · W33</x:v>
+      </x:c>
+      <x:c r="H94" s="24" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>

--- a/outputs/CMS_Guia_Operativa_v2.xlsx
+++ b/outputs/CMS_Guia_Operativa_v2.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="R21881d74f2f24d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contenidos" sheetId="2" r:id="R439fcb0a62294f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectores" sheetId="3" r:id="R2f66dd6dc8c540cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones" sheetId="4" r:id="R8fc7c5098b29460b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="5" r:id="R9fe163e952894f63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasos" sheetId="6" r:id="R9c4009c8ef314d3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="7" r:id="R104706e1ecef4913"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normas" sheetId="8" r:id="Rccc91794fa8744c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios" sheetId="9" r:id="Recf9a0b087514f56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria" sheetId="10" r:id="R9ccba15d76bb4a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanas" sheetId="11" r:id="R6cee23033a8344ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="Ra640af9e34f546e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contenidos" sheetId="2" r:id="Raa7680d87e8841cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectores" sheetId="3" r:id="R04b8f1b79eb840d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones" sheetId="4" r:id="Rdc1a3930e7794089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="5" r:id="R71c3dd12475e4607"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasos" sheetId="6" r:id="R69e02caafb2a476e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="7" r:id="Rd029594383014b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normas" sheetId="8" r:id="Re62a985189af4e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios" sheetId="9" r:id="R7f8387773d2e46fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria" sheetId="10" r:id="R5cf12da4164e4391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanas" sheetId="11" r:id="R0f9304dc4b9646ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -74,7 +74,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -124,6 +124,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF6FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -181,7 +186,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -262,6 +267,20 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1043,6 +1062,57 @@
         <x:v>Unicorn prioritario; lavanda separada</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="45" t="str">
+        <x:v>SALSA_PUMP_CBS</x:v>
+      </x:c>
+      <x:c r="B16" s="45" t="str">
+        <x:v>6 y 8 pumps CBS</x:v>
+      </x:c>
+      <x:c r="C16" s="45" t="str">
+        <x:v>Dosificador identificado</x:v>
+      </x:c>
+      <x:c r="D16" s="45" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E16" s="45" t="str">
+        <x:v>Evita confusión con pump espresso</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="46" t="str">
+        <x:v>EVALUACION_UNICORN</x:v>
+      </x:c>
+      <x:c r="B17" s="46" t="str">
+        <x:v>5 reactivos</x:v>
+      </x:c>
+      <x:c r="C17" s="46" t="str">
+        <x:v>Retroalimentación inmediata</x:v>
+      </x:c>
+      <x:c r="D17" s="46" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E17" s="46" t="str">
+        <x:v>Validar conocimiento al terminar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="47" t="str">
+        <x:v>PWA_IOS</x:v>
+      </x:c>
+      <x:c r="B18" s="47" t="str">
+        <x:v>Instalación guiada</x:v>
+      </x:c>
+      <x:c r="C18" s="47" t="str">
+        <x:v>Compartir &gt; pantalla de inicio</x:v>
+      </x:c>
+      <x:c r="D18" s="47" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E18" s="47" t="str">
+        <x:v>Disponible desde navegación</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
@@ -4777,13 +4847,13 @@
         <x:v>Agrega mocha blanco</x:v>
       </x:c>
       <x:c r="D50" s="22" t="str">
-        <x:v>Coloca la salsa de mocha blanco en una jarra vaporizadora.</x:v>
+        <x:v>Coloca la salsa de mocha blanco en una jarra vaporizadora usando el pump CBS.</x:v>
       </x:c>
       <x:c r="E50" s="22" t="str">
         <x:v>sauce</x:v>
       </x:c>
       <x:c r="F50" s="22" t="str">
-        <x:v>GRANDE=6 pumps</x:v>
+        <x:v>GRANDE=6 pumps CBS</x:v>
       </x:c>
       <x:c r="G50" s="22" t="n">
         <x:v>0</x:v>
@@ -4865,13 +4935,13 @@
         <x:v>Agrega mocha blanco</x:v>
       </x:c>
       <x:c r="D53" s="23" t="str">
-        <x:v>Añade más salsa de mocha blanco a la misma preparación.</x:v>
+        <x:v>Añade más salsa de mocha blanco con el pump CBS a la misma preparación.</x:v>
       </x:c>
       <x:c r="E53" s="23" t="str">
         <x:v>sauce</x:v>
       </x:c>
       <x:c r="F53" s="23" t="str">
-        <x:v>GRANDE=8 pumps</x:v>
+        <x:v>GRANDE=8 pumps CBS</x:v>
       </x:c>
       <x:c r="G53" s="23" t="n">
         <x:v>0</x:v>

--- a/outputs/CMS_Guia_Operativa_v2.xlsx
+++ b/outputs/CMS_Guia_Operativa_v2.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="Ra640af9e34f546e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contenidos" sheetId="2" r:id="Raa7680d87e8841cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectores" sheetId="3" r:id="R04b8f1b79eb840d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones" sheetId="4" r:id="Rdc1a3930e7794089"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="5" r:id="R71c3dd12475e4607"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasos" sheetId="6" r:id="R69e02caafb2a476e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="7" r:id="Rd029594383014b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normas" sheetId="8" r:id="Re62a985189af4e06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios" sheetId="9" r:id="R7f8387773d2e46fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria" sheetId="10" r:id="R5cf12da4164e4391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanas" sheetId="11" r:id="R0f9304dc4b9646ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="Rb170682d07504479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contenidos" sheetId="2" r:id="R6e0dbe5e3f7b4e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectores" sheetId="3" r:id="R94e13096883e431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones" sheetId="4" r:id="R08819e2c4af74440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="5" r:id="R187e8b73e3504b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasos" sheetId="6" r:id="R1d57fd5369bf4486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="7" r:id="R1f50cd32c59440a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normas" sheetId="8" r:id="R6c747e243e444af9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios" sheetId="9" r:id="Re5a021d0b8254508"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria" sheetId="10" r:id="R4b354fafe3a346a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanas" sheetId="11" r:id="R7418bd384a454001"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1245,9 +1245,7 @@
       <x:c r="J5" s="38" t="str">
         <x:v>assets/campaigns/unicorn-buenas-practicas.webp</x:v>
       </x:c>
-      <x:c r="K5" s="38" t="str">
-        <x:v>assets/campaigns/unicorn-concurso.webp</x:v>
-      </x:c>
+      <x:c r="K5" s="38"/>
       <x:c r="L5" s="39" t="str">
         <x:v>SI</x:v>
       </x:c>

--- a/outputs/CMS_Guia_Operativa_v2.xlsx
+++ b/outputs/CMS_Guia_Operativa_v2.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="Rb170682d07504479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contenidos" sheetId="2" r:id="R6e0dbe5e3f7b4e09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectores" sheetId="3" r:id="R94e13096883e431d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones" sheetId="4" r:id="R08819e2c4af74440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="5" r:id="R187e8b73e3504b83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasos" sheetId="6" r:id="R1d57fd5369bf4486"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="7" r:id="R1f50cd32c59440a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normas" sheetId="8" r:id="R6c747e243e444af9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios" sheetId="9" r:id="Re5a021d0b8254508"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria" sheetId="10" r:id="R4b354fafe3a346a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanas" sheetId="11" r:id="R7418bd384a454001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="R640336c1367344c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contenidos" sheetId="2" r:id="Rf4d8562232b147be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selectores" sheetId="3" r:id="R1272f58fda704097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones" sheetId="4" r:id="R68a593960fe04357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="5" r:id="R8bb388e2cf734cc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasos" sheetId="6" r:id="R85abdb0da1234c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="7" r:id="R9c7dc79db4ab4aef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normas" sheetId="8" r:id="R33d81b1d2e084179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios" sheetId="9" r:id="Re918c7fdd0204c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria" sheetId="10" r:id="R0828410ed9c54231"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanas" sheetId="11" r:id="R68a425dab31e448d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1245,7 +1245,9 @@
       <x:c r="J5" s="38" t="str">
         <x:v>assets/campaigns/unicorn-buenas-practicas.webp</x:v>
       </x:c>
-      <x:c r="K5" s="38"/>
+      <x:c r="K5" s="38" t="str">
+        <x:v>assets/campaigns/unicorn-concurso.webp</x:v>
+      </x:c>
       <x:c r="L5" s="39" t="str">
         <x:v>SI</x:v>
       </x:c>
